--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -166,7 +166,7 @@
     <t>Mid-Ohio Regional Planning Commission</t>
   </si>
   <si>
-    <t>2025</t>
+    <t>2026</t>
   </si>
   <si>
     <t>annually</t>
